--- a/informe-compras-evolti/INFORME DE COMPRAS - POLARIS 4 (MINIGRANJA).xlsx
+++ b/informe-compras-evolti/INFORME DE COMPRAS - POLARIS 4 (MINIGRANJA).xlsx
@@ -372,12 +372,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Por categoría'!$I$6:$I$21</f>
+              <f>'Por categoría'!$I$6:$I$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Por categoría'!$J$6:$J$21</f>
+              <f>'Por categoría'!$J$6:$J$20</f>
             </numRef>
           </val>
         </ser>
@@ -535,7 +535,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="3600000"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C16" s="13" t="n"/>
       <c r="D16" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J52"/>
+  <dimension ref="B2:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1262,11 +1262,11 @@
         <v/>
       </c>
       <c r="I7">
-        <f>B17</f>
+        <f>B18</f>
         <v/>
       </c>
       <c r="J7">
-        <f>D17</f>
+        <f>D18</f>
         <v/>
       </c>
     </row>
@@ -1294,11 +1294,11 @@
         <v/>
       </c>
       <c r="I8">
-        <f>B19</f>
+        <f>B20</f>
         <v/>
       </c>
       <c r="J8">
-        <f>D19</f>
+        <f>D20</f>
         <v/>
       </c>
     </row>
@@ -1326,11 +1326,11 @@
         <v/>
       </c>
       <c r="I9">
-        <f>B22</f>
+        <f>B23</f>
         <v/>
       </c>
       <c r="J9">
-        <f>D22</f>
+        <f>D23</f>
         <v/>
       </c>
     </row>
@@ -1358,11 +1358,11 @@
         <v/>
       </c>
       <c r="I10">
-        <f>B24</f>
+        <f>B25</f>
         <v/>
       </c>
       <c r="J10">
-        <f>D24</f>
+        <f>D25</f>
         <v/>
       </c>
     </row>
@@ -1390,11 +1390,11 @@
         <v/>
       </c>
       <c r="I11">
-        <f>B26</f>
+        <f>B27</f>
         <v/>
       </c>
       <c r="J11">
-        <f>D26</f>
+        <f>D27</f>
         <v/>
       </c>
     </row>
@@ -1422,11 +1422,11 @@
         <v/>
       </c>
       <c r="I12">
-        <f>B29</f>
+        <f>B30</f>
         <v/>
       </c>
       <c r="J12">
-        <f>D29</f>
+        <f>D30</f>
         <v/>
       </c>
     </row>
@@ -1454,11 +1454,11 @@
         <v/>
       </c>
       <c r="I13">
-        <f>B32</f>
+        <f>B33</f>
         <v/>
       </c>
       <c r="J13">
-        <f>D32</f>
+        <f>D33</f>
         <v/>
       </c>
     </row>
@@ -1486,11 +1486,11 @@
         <v/>
       </c>
       <c r="I14">
-        <f>B35</f>
+        <f>B36</f>
         <v/>
       </c>
       <c r="J14">
-        <f>D35</f>
+        <f>D36</f>
         <v/>
       </c>
     </row>
@@ -1518,11 +1518,11 @@
         <v/>
       </c>
       <c r="I15">
-        <f>B37</f>
+        <f>B38</f>
         <v/>
       </c>
       <c r="J15">
-        <f>D37</f>
+        <f>D38</f>
         <v/>
       </c>
     </row>
@@ -1550,139 +1550,139 @@
         <v/>
       </c>
       <c r="I16">
-        <f>B40</f>
+        <f>B41</f>
         <v/>
       </c>
       <c r="J16">
-        <f>D40</f>
+        <f>D41</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D17" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B6,Detalle!$G$2:$G$326,$C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B6,Detalle!$G$2:$G$326,$C17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="28">
+        <f>D17+E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D17/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>B43</f>
+        <v/>
+      </c>
+      <c r="J17">
+        <f>D43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>C. Estructura Solar</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="21">
-        <f>D17+E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D17/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-      <c r="I17">
-        <f>B42</f>
-        <v/>
-      </c>
-      <c r="J17">
-        <f>D42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D18" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B17,Detalle!$G$2:$G$326,$C18)</f>
-        <v/>
-      </c>
-      <c r="E18" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B17,Detalle!$G$2:$G$326,$C18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="28">
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
         <f>D18+E18</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D18/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
       <c r="I18">
-        <f>B44</f>
+        <f>B45</f>
         <v/>
       </c>
       <c r="J18">
-        <f>D44</f>
+        <f>D45</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D19" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B18,Detalle!$G$2:$G$326,$C19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B18,Detalle!$G$2:$G$326,$C19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="28">
+        <f>D19+E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D19/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>B47</f>
+        <v/>
+      </c>
+      <c r="J19">
+        <f>D47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Set (Electrico) Suministro</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B19)</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="21">
-        <f>D19+E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D19/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-      <c r="I19">
-        <f>B46</f>
-        <v/>
-      </c>
-      <c r="J19">
-        <f>D46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D20" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B19,Detalle!$G$2:$G$326,$C20)</f>
-        <v/>
-      </c>
-      <c r="E20" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B19,Detalle!$G$2:$G$326,$C20)</f>
-        <v/>
-      </c>
-      <c r="F20" s="28">
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
         <f>D20+E20</f>
         <v/>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D20/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
       <c r="I20">
-        <f>B48</f>
+        <f>B49</f>
         <v/>
       </c>
       <c r="J20">
-        <f>D48</f>
+        <f>D49</f>
         <v/>
       </c>
     </row>
@@ -1690,15 +1690,15 @@
       <c r="B21" s="26" t="n"/>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>Set (Electrico)Servicio</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="D21" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B19,Detalle!$G$2:$G$326,$C21)</f>
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B20,Detalle!$G$2:$G$326,$C21)</f>
         <v/>
       </c>
       <c r="E21" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B19,Detalle!$G$2:$G$326,$C21)</f>
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B20,Detalle!$G$2:$G$326,$C21)</f>
         <v/>
       </c>
       <c r="F21" s="28">
@@ -1709,155 +1709,147 @@
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D21/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
-      <c r="I21">
-        <f>B50</f>
-        <v/>
-      </c>
-      <c r="J21">
-        <f>D50</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Set (Electrico)Servicio</t>
+        </is>
+      </c>
+      <c r="D22" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B20,Detalle!$G$2:$G$326,$C22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B20,Detalle!$G$2:$G$326,$C22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>D22+E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D22/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>C. Inversores</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B22)</f>
-        <v/>
-      </c>
-      <c r="E22" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="21">
-        <f>D22+E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D22/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D23" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B22,Detalle!$G$2:$G$326,$C23)</f>
-        <v/>
-      </c>
-      <c r="E23" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B22,Detalle!$G$2:$G$326,$C23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="28">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="21">
         <f>D23+E23</f>
         <v/>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D23/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D24" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B23,Detalle!$G$2:$G$326,$C24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B23,Detalle!$G$2:$G$326,$C24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="28">
+        <f>D24+E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D24/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>C. Material Micropilotaje</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B24)</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="21">
-        <f>D24+E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D24/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="26" t="n"/>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D25" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B24,Detalle!$G$2:$G$326,$C25)</f>
-        <v/>
-      </c>
-      <c r="E25" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B24,Detalle!$G$2:$G$326,$C25)</f>
-        <v/>
-      </c>
-      <c r="F25" s="28">
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
         <f>D25+E25</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D25/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D26" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B25,Detalle!$G$2:$G$326,$C26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B25,Detalle!$G$2:$G$326,$C26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="28">
+        <f>D26+E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D26/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Set (Civil) Suministro</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B26)</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B26)</f>
-        <v/>
-      </c>
-      <c r="F26" s="21">
-        <f>D26+E26</f>
-        <v/>
-      </c>
-      <c r="G26" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D26/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>Set (Civil) Servicio</t>
-        </is>
-      </c>
-      <c r="D27" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B26,Detalle!$G$2:$G$326,$C27)</f>
-        <v/>
-      </c>
-      <c r="E27" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B26,Detalle!$G$2:$G$326,$C27)</f>
-        <v/>
-      </c>
-      <c r="F27" s="28">
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B27)</f>
+        <v/>
+      </c>
+      <c r="F27" s="21">
         <f>D27+E27</f>
         <v/>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D27/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
@@ -1866,15 +1858,15 @@
       <c r="B28" s="26" t="n"/>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>Set (Civil) Servicio</t>
         </is>
       </c>
       <c r="D28" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B26,Detalle!$G$2:$G$326,$C28)</f>
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B27,Detalle!$G$2:$G$326,$C28)</f>
         <v/>
       </c>
       <c r="E28" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B26,Detalle!$G$2:$G$326,$C28)</f>
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B27,Detalle!$G$2:$G$326,$C28)</f>
         <v/>
       </c>
       <c r="F28" s="28">
@@ -1887,49 +1879,49 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D29" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B27,Detalle!$G$2:$G$326,$C29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B27,Detalle!$G$2:$G$326,$C29)</f>
+        <v/>
+      </c>
+      <c r="F29" s="28">
+        <f>D29+E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D29/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>Cajas De Paso</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B29)</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B29)</f>
-        <v/>
-      </c>
-      <c r="F29" s="21">
-        <f>D29+E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D29/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D30" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B29,Detalle!$G$2:$G$326,$C30)</f>
-        <v/>
-      </c>
-      <c r="E30" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B29,Detalle!$G$2:$G$326,$C30)</f>
-        <v/>
-      </c>
-      <c r="F30" s="28">
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B30)</f>
+        <v/>
+      </c>
+      <c r="F30" s="21">
         <f>D30+E30</f>
         <v/>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D30/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
@@ -1938,15 +1930,15 @@
       <c r="B31" s="26" t="n"/>
       <c r="C31" s="27" t="inlineStr">
         <is>
-          <t>Transportes</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="D31" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B29,Detalle!$G$2:$G$326,$C31)</f>
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B30,Detalle!$G$2:$G$326,$C31)</f>
         <v/>
       </c>
       <c r="E31" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B29,Detalle!$G$2:$G$326,$C31)</f>
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B30,Detalle!$G$2:$G$326,$C31)</f>
         <v/>
       </c>
       <c r="F31" s="28">
@@ -1959,49 +1951,49 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>Transportes</t>
+        </is>
+      </c>
+      <c r="D32" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B30,Detalle!$G$2:$G$326,$C32)</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B30,Detalle!$G$2:$G$326,$C32)</f>
+        <v/>
+      </c>
+      <c r="F32" s="28">
+        <f>D32+E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D32/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>Montaje Eléctrico</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B32)</f>
-        <v/>
-      </c>
-      <c r="E32" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B32)</f>
-        <v/>
-      </c>
-      <c r="F32" s="21">
-        <f>D32+E32</f>
-        <v/>
-      </c>
-      <c r="G32" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D32/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>Set (Electrico)Servicio</t>
-        </is>
-      </c>
-      <c r="D33" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B32,Detalle!$G$2:$G$326,$C33)</f>
-        <v/>
-      </c>
-      <c r="E33" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B32,Detalle!$G$2:$G$326,$C33)</f>
-        <v/>
-      </c>
-      <c r="F33" s="28">
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B33)</f>
+        <v/>
+      </c>
+      <c r="F33" s="21">
         <f>D33+E33</f>
         <v/>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D33/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
@@ -2010,15 +2002,15 @@
       <c r="B34" s="26" t="n"/>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>Set (Electrico)Servicio</t>
         </is>
       </c>
       <c r="D34" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B32,Detalle!$G$2:$G$326,$C34)</f>
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B33,Detalle!$G$2:$G$326,$C34)</f>
         <v/>
       </c>
       <c r="E34" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B32,Detalle!$G$2:$G$326,$C34)</f>
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B33,Detalle!$G$2:$G$326,$C34)</f>
         <v/>
       </c>
       <c r="F34" s="28">
@@ -2031,97 +2023,97 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D35" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B33,Detalle!$G$2:$G$326,$C35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B33,Detalle!$G$2:$G$326,$C35)</f>
+        <v/>
+      </c>
+      <c r="F35" s="28">
+        <f>D35+E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D35/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Gastos Administrativos</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B35)</f>
-        <v/>
-      </c>
-      <c r="E35" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B35)</f>
-        <v/>
-      </c>
-      <c r="F35" s="21">
-        <f>D35+E35</f>
-        <v/>
-      </c>
-      <c r="G35" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D35/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="26" t="n"/>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B36)</f>
+        <v/>
+      </c>
+      <c r="E36" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B36)</f>
+        <v/>
+      </c>
+      <c r="F36" s="21">
+        <f>D36+E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="25">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D36/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="27" t="inlineStr">
         <is>
           <t>Logística Viáticos</t>
         </is>
       </c>
-      <c r="D36" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B35,Detalle!$G$2:$G$326,$C36)</f>
-        <v/>
-      </c>
-      <c r="E36" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B35,Detalle!$G$2:$G$326,$C36)</f>
-        <v/>
-      </c>
-      <c r="F36" s="28">
-        <f>D36+E36</f>
-        <v/>
-      </c>
-      <c r="G36" s="29">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D36/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="20" t="inlineStr">
+      <c r="D37" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B36,Detalle!$G$2:$G$326,$C37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B36,Detalle!$G$2:$G$326,$C37)</f>
+        <v/>
+      </c>
+      <c r="F37" s="28">
+        <f>D37+E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D37/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>C. Canalizaciones</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B37)</f>
-        <v/>
-      </c>
-      <c r="E37" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B37)</f>
-        <v/>
-      </c>
-      <c r="F37" s="21">
-        <f>D37+E37</f>
-        <v/>
-      </c>
-      <c r="G37" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D37/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="26" t="n"/>
-      <c r="C38" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D38" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B37,Detalle!$G$2:$G$326,$C38)</f>
-        <v/>
-      </c>
-      <c r="E38" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B37,Detalle!$G$2:$G$326,$C38)</f>
-        <v/>
-      </c>
-      <c r="F38" s="28">
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B38)</f>
+        <v/>
+      </c>
+      <c r="F38" s="21">
         <f>D38+E38</f>
         <v/>
       </c>
-      <c r="G38" s="29">
+      <c r="G38" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D38/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
@@ -2130,15 +2122,15 @@
       <c r="B39" s="26" t="n"/>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>Instalación De Tuberías Ac, Dc Y Tierra</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="D39" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B37,Detalle!$G$2:$G$326,$C39)</f>
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B38,Detalle!$G$2:$G$326,$C39)</f>
         <v/>
       </c>
       <c r="E39" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B37,Detalle!$G$2:$G$326,$C39)</f>
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B38,Detalle!$G$2:$G$326,$C39)</f>
         <v/>
       </c>
       <c r="F39" s="28">
@@ -2151,313 +2143,289 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>Instalación De Tuberías Ac, Dc Y Tierra</t>
+        </is>
+      </c>
+      <c r="D40" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B38,Detalle!$G$2:$G$326,$C40)</f>
+        <v/>
+      </c>
+      <c r="E40" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B38,Detalle!$G$2:$G$326,$C40)</f>
+        <v/>
+      </c>
+      <c r="F40" s="28">
+        <f>D40+E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D40/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>Armado Mesas Fv</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B40)</f>
-        <v/>
-      </c>
-      <c r="E40" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B40)</f>
-        <v/>
-      </c>
-      <c r="F40" s="21">
-        <f>D40+E40</f>
-        <v/>
-      </c>
-      <c r="G40" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D40/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="26" t="n"/>
-      <c r="C41" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D41" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B40,Detalle!$G$2:$G$326,$C41)</f>
-        <v/>
-      </c>
-      <c r="E41" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B40,Detalle!$G$2:$G$326,$C41)</f>
-        <v/>
-      </c>
-      <c r="F41" s="28">
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B41)</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B41)</f>
+        <v/>
+      </c>
+      <c r="F41" s="21">
         <f>D41+E41</f>
         <v/>
       </c>
-      <c r="G41" s="29">
+      <c r="G41" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D41/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D42" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B41,Detalle!$G$2:$G$326,$C42)</f>
+        <v/>
+      </c>
+      <c r="E42" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B41,Detalle!$G$2:$G$326,$C42)</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>D42+E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D42/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>9-Legalización</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B42)</f>
-        <v/>
-      </c>
-      <c r="E42" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B42)</f>
-        <v/>
-      </c>
-      <c r="F42" s="21">
-        <f>D42+E42</f>
-        <v/>
-      </c>
-      <c r="G42" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D42/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>9.1 -RETIE GD</t>
-        </is>
-      </c>
-      <c r="D43" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B42,Detalle!$G$2:$G$326,$C43)</f>
-        <v/>
-      </c>
-      <c r="E43" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B42,Detalle!$G$2:$G$326,$C43)</f>
-        <v/>
-      </c>
-      <c r="F43" s="28">
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B43)</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B43)</f>
+        <v/>
+      </c>
+      <c r="F43" s="21">
         <f>D43+E43</f>
         <v/>
       </c>
-      <c r="G43" s="29">
+      <c r="G43" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D43/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="26" t="n"/>
+      <c r="C44" s="27" t="inlineStr">
+        <is>
+          <t>9.1 -Retie Gd</t>
+        </is>
+      </c>
+      <c r="D44" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B43,Detalle!$G$2:$G$326,$C44)</f>
+        <v/>
+      </c>
+      <c r="E44" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B43,Detalle!$G$2:$G$326,$C44)</f>
+        <v/>
+      </c>
+      <c r="F44" s="28">
+        <f>D44+E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D44/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>C. Cableado Ac</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B44)</f>
-        <v/>
-      </c>
-      <c r="E44" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B44)</f>
-        <v/>
-      </c>
-      <c r="F44" s="21">
-        <f>D44+E44</f>
-        <v/>
-      </c>
-      <c r="G44" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D44/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="26" t="n"/>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D45" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B44,Detalle!$G$2:$G$326,$C45)</f>
-        <v/>
-      </c>
-      <c r="E45" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B44,Detalle!$G$2:$G$326,$C45)</f>
-        <v/>
-      </c>
-      <c r="F45" s="28">
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B45)</f>
+        <v/>
+      </c>
+      <c r="E45" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B45)</f>
+        <v/>
+      </c>
+      <c r="F45" s="21">
         <f>D45+E45</f>
         <v/>
       </c>
-      <c r="G45" s="29">
+      <c r="G45" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D45/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="26" t="n"/>
+      <c r="C46" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D46" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B45,Detalle!$G$2:$G$326,$C46)</f>
+        <v/>
+      </c>
+      <c r="E46" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B45,Detalle!$G$2:$G$326,$C46)</f>
+        <v/>
+      </c>
+      <c r="F46" s="28">
+        <f>D46+E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D46/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>C. Cableado Dc</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B46)</f>
-        <v/>
-      </c>
-      <c r="E46" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B46)</f>
-        <v/>
-      </c>
-      <c r="F46" s="21">
-        <f>D46+E46</f>
-        <v/>
-      </c>
-      <c r="G46" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D46/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="26" t="n"/>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D47" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B46,Detalle!$G$2:$G$326,$C47)</f>
-        <v/>
-      </c>
-      <c r="E47" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B46,Detalle!$G$2:$G$326,$C47)</f>
-        <v/>
-      </c>
-      <c r="F47" s="28">
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B47)</f>
+        <v/>
+      </c>
+      <c r="E47" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B47)</f>
+        <v/>
+      </c>
+      <c r="F47" s="21">
         <f>D47+E47</f>
         <v/>
       </c>
-      <c r="G47" s="29">
+      <c r="G47" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D47/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="26" t="n"/>
+      <c r="C48" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D48" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B47,Detalle!$G$2:$G$326,$C48)</f>
+        <v/>
+      </c>
+      <c r="E48" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B47,Detalle!$G$2:$G$326,$C48)</f>
+        <v/>
+      </c>
+      <c r="F48" s="28">
+        <f>D48+E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="29">
+        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D48/SUM(Detalle!$K$2:$K$326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>C. Cableado Tierra</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B48)</f>
-        <v/>
-      </c>
-      <c r="E48" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B48)</f>
-        <v/>
-      </c>
-      <c r="F48" s="21">
-        <f>D48+E48</f>
-        <v/>
-      </c>
-      <c r="G48" s="25">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D48/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="26" t="n"/>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D49" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B48,Detalle!$G$2:$G$326,$C49)</f>
-        <v/>
-      </c>
-      <c r="E49" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B48,Detalle!$G$2:$G$326,$C49)</f>
-        <v/>
-      </c>
-      <c r="F49" s="28">
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="21">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B49)</f>
+        <v/>
+      </c>
+      <c r="E49" s="21">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B49)</f>
+        <v/>
+      </c>
+      <c r="F49" s="21">
         <f>D49+E49</f>
         <v/>
       </c>
-      <c r="G49" s="29">
+      <c r="G49" s="25">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D49/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t>SERVICIO</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="21">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B50)</f>
-        <v/>
-      </c>
-      <c r="E50" s="21">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B50)</f>
-        <v/>
-      </c>
-      <c r="F50" s="21">
+      <c r="B50" s="26" t="n"/>
+      <c r="C50" s="27" t="inlineStr">
+        <is>
+          <t>(Sin Subgrupo)</t>
+        </is>
+      </c>
+      <c r="D50" s="28">
+        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B49,Detalle!$G$2:$G$326,$C50)</f>
+        <v/>
+      </c>
+      <c r="E50" s="28">
+        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B49,Detalle!$G$2:$G$326,$C50)</f>
+        <v/>
+      </c>
+      <c r="F50" s="28">
         <f>D50+E50</f>
         <v/>
       </c>
-      <c r="G50" s="25">
+      <c r="G50" s="29">
         <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D50/SUM(Detalle!$K$2:$K$326))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="26" t="n"/>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>(sin subgrupo)</t>
-        </is>
-      </c>
-      <c r="D51" s="28">
-        <f>SUMIFS(Detalle!$K$2:$K$326,Detalle!$F$2:$F$326,$B50,Detalle!$G$2:$G$326,$C51)</f>
-        <v/>
-      </c>
-      <c r="E51" s="28">
-        <f>SUMIFS(Detalle!$M$2:$M$326,Detalle!$F$2:$F$326,$B50,Detalle!$G$2:$G$326,$C51)</f>
-        <v/>
-      </c>
-      <c r="F51" s="28">
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="31">
+        <f>SUM(Detalle!$K$2:$K$326)</f>
+        <v/>
+      </c>
+      <c r="E51" s="31">
+        <f>SUM(Detalle!$M$2:$M$326)</f>
+        <v/>
+      </c>
+      <c r="F51" s="31">
         <f>D51+E51</f>
         <v/>
       </c>
-      <c r="G51" s="29">
-        <f>IF(SUM(Detalle!$K$2:$K$326)=0,0,D51/SUM(Detalle!$K$2:$K$326))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C52" s="30" t="n"/>
-      <c r="D52" s="31">
-        <f>D6+D17+D19+D22+D24+D26+D29+D32+D35+D37+D40+D42+D44+D46+D48+D50</f>
-        <v/>
-      </c>
-      <c r="E52" s="31">
-        <f>E6+E17+E19+E22+E24+E26+E29+E32+E35+E37+E40+E42+E44+E46+E48+E50</f>
-        <v/>
-      </c>
-      <c r="F52" s="31">
-        <f>D52+E52</f>
-        <v/>
-      </c>
-      <c r="G52" s="32" t="n">
+      <c r="G51" s="32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3255,11 +3223,11 @@
         <v/>
       </c>
       <c r="D33" s="31">
-        <f>SUM(D7:D32)</f>
+        <f>SUM(Detalle!$K$2:$K$326)</f>
         <v/>
       </c>
       <c r="E33" s="31">
-        <f>SUM(E7:E32)</f>
+        <f>SUM(Detalle!$M$2:$M$326)</f>
         <v/>
       </c>
       <c r="F33" s="31">
@@ -9504,11 +9472,11 @@
         </is>
       </c>
       <c r="C39" s="21">
-        <f>SUM(C6:C38)</f>
+        <f>SUM(Detalle!$K$2:$K$326)</f>
         <v/>
       </c>
       <c r="D39" s="21">
-        <f>SUM(D6:D38)</f>
+        <f>SUM(Detalle!$M$2:$M$326)</f>
         <v/>
       </c>
       <c r="E39" s="21">
@@ -12399,7 +12367,7 @@
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H32" s="16" t="inlineStr">
@@ -12486,7 +12454,7 @@
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
@@ -12739,7 +12707,7 @@
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>9.1 -RETIE GD</t>
+          <t>9.1 -Retie Gd</t>
         </is>
       </c>
       <c r="H36" s="16" t="inlineStr">
@@ -12826,7 +12794,7 @@
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H37" s="18" t="inlineStr">
@@ -12913,7 +12881,7 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H38" s="16" t="inlineStr">
@@ -13419,7 +13387,7 @@
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H44" s="16" t="inlineStr">
@@ -13506,7 +13474,7 @@
       </c>
       <c r="G45" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H45" s="18" t="inlineStr">
@@ -13589,7 +13557,7 @@
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H46" s="16" t="inlineStr">
@@ -14759,7 +14727,7 @@
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H60" s="16" t="inlineStr">
@@ -14842,7 +14810,7 @@
       </c>
       <c r="G61" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H61" s="18" t="inlineStr">
@@ -14925,7 +14893,7 @@
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H62" s="16" t="inlineStr">
@@ -15008,7 +14976,7 @@
       </c>
       <c r="G63" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H63" s="18" t="inlineStr">
@@ -15091,7 +15059,7 @@
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H64" s="16" t="inlineStr">
@@ -15174,7 +15142,7 @@
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H65" s="18" t="inlineStr">
@@ -15257,7 +15225,7 @@
       </c>
       <c r="G66" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H66" s="16" t="inlineStr">
@@ -15340,7 +15308,7 @@
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H67" s="18" t="inlineStr">
@@ -15423,7 +15391,7 @@
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H68" s="16" t="inlineStr">
@@ -15506,7 +15474,7 @@
       </c>
       <c r="G69" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H69" s="18" t="inlineStr">
@@ -15589,7 +15557,7 @@
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H70" s="16" t="inlineStr">
@@ -15672,7 +15640,7 @@
       </c>
       <c r="G71" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H71" s="18" t="inlineStr">
@@ -15755,7 +15723,7 @@
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H72" s="16" t="inlineStr">
@@ -15838,7 +15806,7 @@
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H73" s="18" t="inlineStr">
@@ -15921,7 +15889,7 @@
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H74" s="16" t="inlineStr">
@@ -16004,7 +15972,7 @@
       </c>
       <c r="G75" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H75" s="18" t="inlineStr">
@@ -16087,7 +16055,7 @@
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H76" s="16" t="inlineStr">
@@ -16170,7 +16138,7 @@
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H77" s="18" t="inlineStr">
@@ -16253,7 +16221,7 @@
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H78" s="16" t="inlineStr">
@@ -16336,7 +16304,7 @@
       </c>
       <c r="G79" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H79" s="18" t="inlineStr">
@@ -16419,7 +16387,7 @@
       </c>
       <c r="G80" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H80" s="16" t="inlineStr">
@@ -16502,7 +16470,7 @@
       </c>
       <c r="G81" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H81" s="18" t="inlineStr">
@@ -16585,7 +16553,7 @@
       </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H82" s="16" t="inlineStr">
@@ -16668,7 +16636,7 @@
       </c>
       <c r="G83" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H83" s="18" t="inlineStr">
@@ -16751,7 +16719,7 @@
       </c>
       <c r="G84" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H84" s="16" t="inlineStr">
@@ -16834,7 +16802,7 @@
       </c>
       <c r="G85" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H85" s="18" t="inlineStr">
@@ -16917,7 +16885,7 @@
       </c>
       <c r="G86" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H86" s="16" t="inlineStr">
@@ -17000,7 +16968,7 @@
       </c>
       <c r="G87" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H87" s="18" t="inlineStr">
@@ -17083,7 +17051,7 @@
       </c>
       <c r="G88" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H88" s="16" t="inlineStr">
@@ -17166,7 +17134,7 @@
       </c>
       <c r="G89" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H89" s="18" t="inlineStr">
@@ -17249,7 +17217,7 @@
       </c>
       <c r="G90" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H90" s="16" t="inlineStr">
@@ -17332,7 +17300,7 @@
       </c>
       <c r="G91" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H91" s="18" t="inlineStr">
@@ -17415,7 +17383,7 @@
       </c>
       <c r="G92" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H92" s="16" t="inlineStr">
@@ -17498,7 +17466,7 @@
       </c>
       <c r="G93" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H93" s="18" t="inlineStr">
@@ -17581,7 +17549,7 @@
       </c>
       <c r="G94" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H94" s="16" t="inlineStr">
@@ -17664,7 +17632,7 @@
       </c>
       <c r="G95" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H95" s="18" t="inlineStr">
@@ -17747,7 +17715,7 @@
       </c>
       <c r="G96" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H96" s="16" t="inlineStr">
@@ -17830,7 +17798,7 @@
       </c>
       <c r="G97" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H97" s="18" t="inlineStr">
@@ -17913,7 +17881,7 @@
       </c>
       <c r="G98" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H98" s="16" t="inlineStr">
@@ -17996,7 +17964,7 @@
       </c>
       <c r="G99" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H99" s="18" t="inlineStr">
@@ -18079,7 +18047,7 @@
       </c>
       <c r="G100" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H100" s="16" t="inlineStr">
@@ -18162,7 +18130,7 @@
       </c>
       <c r="G101" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H101" s="18" t="inlineStr">
@@ -18245,7 +18213,7 @@
       </c>
       <c r="G102" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H102" s="16" t="inlineStr">
@@ -18328,7 +18296,7 @@
       </c>
       <c r="G103" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H103" s="18" t="inlineStr">
@@ -18411,7 +18379,7 @@
       </c>
       <c r="G104" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H104" s="16" t="inlineStr">
@@ -18494,7 +18462,7 @@
       </c>
       <c r="G105" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H105" s="18" t="inlineStr">
@@ -18577,7 +18545,7 @@
       </c>
       <c r="G106" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H106" s="16" t="inlineStr">
@@ -18660,7 +18628,7 @@
       </c>
       <c r="G107" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H107" s="18" t="inlineStr">
@@ -18743,7 +18711,7 @@
       </c>
       <c r="G108" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H108" s="16" t="inlineStr">
@@ -18826,7 +18794,7 @@
       </c>
       <c r="G109" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H109" s="18" t="inlineStr">
@@ -18909,7 +18877,7 @@
       </c>
       <c r="G110" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H110" s="16" t="inlineStr">
@@ -18992,7 +18960,7 @@
       </c>
       <c r="G111" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H111" s="18" t="inlineStr">
@@ -19075,7 +19043,7 @@
       </c>
       <c r="G112" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H112" s="16" t="inlineStr">
@@ -19158,7 +19126,7 @@
       </c>
       <c r="G113" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H113" s="18" t="inlineStr">
@@ -19241,7 +19209,7 @@
       </c>
       <c r="G114" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H114" s="16" t="inlineStr">
@@ -19324,7 +19292,7 @@
       </c>
       <c r="G115" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H115" s="18" t="inlineStr">
@@ -19407,7 +19375,7 @@
       </c>
       <c r="G116" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H116" s="16" t="inlineStr">
@@ -19490,7 +19458,7 @@
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H117" s="18" t="inlineStr">
@@ -19573,7 +19541,7 @@
       </c>
       <c r="G118" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H118" s="16" t="inlineStr">
@@ -19656,7 +19624,7 @@
       </c>
       <c r="G119" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H119" s="18" t="inlineStr">
@@ -19739,7 +19707,7 @@
       </c>
       <c r="G120" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H120" s="16" t="inlineStr">
@@ -19822,7 +19790,7 @@
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H121" s="18" t="inlineStr">
@@ -19905,7 +19873,7 @@
       </c>
       <c r="G122" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H122" s="16" t="inlineStr">
@@ -19988,7 +19956,7 @@
       </c>
       <c r="G123" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H123" s="18" t="inlineStr">
@@ -20071,7 +20039,7 @@
       </c>
       <c r="G124" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H124" s="16" t="inlineStr">
@@ -20154,7 +20122,7 @@
       </c>
       <c r="G125" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H125" s="18" t="inlineStr">
@@ -20237,7 +20205,7 @@
       </c>
       <c r="G126" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H126" s="16" t="inlineStr">
@@ -20320,7 +20288,7 @@
       </c>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H127" s="18" t="inlineStr">
@@ -20403,7 +20371,7 @@
       </c>
       <c r="G128" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H128" s="16" t="inlineStr">
@@ -20486,7 +20454,7 @@
       </c>
       <c r="G129" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H129" s="18" t="inlineStr">
@@ -20569,7 +20537,7 @@
       </c>
       <c r="G130" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H130" s="16" t="inlineStr">
@@ -20652,7 +20620,7 @@
       </c>
       <c r="G131" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H131" s="18" t="inlineStr">
@@ -20735,7 +20703,7 @@
       </c>
       <c r="G132" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H132" s="16" t="inlineStr">
@@ -20818,7 +20786,7 @@
       </c>
       <c r="G133" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H133" s="18" t="inlineStr">
@@ -20901,7 +20869,7 @@
       </c>
       <c r="G134" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H134" s="16" t="inlineStr">
@@ -20984,7 +20952,7 @@
       </c>
       <c r="G135" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H135" s="18" t="inlineStr">
@@ -21067,7 +21035,7 @@
       </c>
       <c r="G136" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H136" s="16" t="inlineStr">
@@ -21150,7 +21118,7 @@
       </c>
       <c r="G137" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H137" s="18" t="inlineStr">
@@ -21233,7 +21201,7 @@
       </c>
       <c r="G138" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H138" s="16" t="inlineStr">
@@ -21316,7 +21284,7 @@
       </c>
       <c r="G139" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H139" s="18" t="inlineStr">
@@ -22079,7 +22047,7 @@
       </c>
       <c r="G148" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H148" s="16" t="inlineStr">
@@ -22913,7 +22881,7 @@
       </c>
       <c r="G158" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H158" s="16" t="inlineStr">
@@ -22996,7 +22964,7 @@
       </c>
       <c r="G159" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H159" s="18" t="inlineStr">
@@ -23083,7 +23051,7 @@
       </c>
       <c r="G160" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H160" s="16" t="inlineStr">
@@ -23415,7 +23383,7 @@
       </c>
       <c r="G164" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H164" s="16" t="inlineStr">
@@ -23996,7 +23964,7 @@
       </c>
       <c r="G171" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H171" s="18" t="inlineStr">
@@ -24079,7 +24047,7 @@
       </c>
       <c r="G172" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H172" s="16" t="inlineStr">
@@ -24332,7 +24300,7 @@
       </c>
       <c r="G175" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H175" s="18" t="inlineStr">
@@ -24419,7 +24387,7 @@
       </c>
       <c r="G176" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H176" s="16" t="inlineStr">
@@ -24502,7 +24470,7 @@
       </c>
       <c r="G177" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H177" s="18" t="inlineStr">
@@ -24585,7 +24553,7 @@
       </c>
       <c r="G178" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H178" s="16" t="inlineStr">
@@ -24668,7 +24636,7 @@
       </c>
       <c r="G179" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H179" s="18" t="inlineStr">
@@ -24751,7 +24719,7 @@
       </c>
       <c r="G180" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H180" s="16" t="inlineStr">
@@ -24834,7 +24802,7 @@
       </c>
       <c r="G181" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H181" s="18" t="inlineStr">
@@ -24917,7 +24885,7 @@
       </c>
       <c r="G182" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H182" s="16" t="inlineStr">
@@ -25083,7 +25051,7 @@
       </c>
       <c r="G184" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H184" s="16" t="inlineStr">
@@ -25166,7 +25134,7 @@
       </c>
       <c r="G185" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H185" s="18" t="inlineStr">
@@ -25249,7 +25217,7 @@
       </c>
       <c r="G186" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H186" s="16" t="inlineStr">
@@ -25589,7 +25557,7 @@
       </c>
       <c r="G190" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H190" s="16" t="inlineStr">
@@ -26916,12 +26884,12 @@
       </c>
       <c r="F206" s="16" t="inlineStr">
         <is>
-          <t>SERVICIO</t>
+          <t>Servicio</t>
         </is>
       </c>
       <c r="G206" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H206" s="16" t="inlineStr">
@@ -27087,7 +27055,7 @@
       </c>
       <c r="G208" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H208" s="16" t="inlineStr">
@@ -27170,7 +27138,7 @@
       </c>
       <c r="G209" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H209" s="18" t="inlineStr">
@@ -27917,7 +27885,7 @@
       </c>
       <c r="G218" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H218" s="16" t="inlineStr">
@@ -28083,7 +28051,7 @@
       </c>
       <c r="G220" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H220" s="16" t="inlineStr">
@@ -31498,7 +31466,7 @@
       </c>
       <c r="G261" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H261" s="18" t="inlineStr">
@@ -31581,7 +31549,7 @@
       </c>
       <c r="G262" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H262" s="16" t="inlineStr">
@@ -32660,7 +32628,7 @@
       </c>
       <c r="G275" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H275" s="18" t="inlineStr">
@@ -32743,7 +32711,7 @@
       </c>
       <c r="G276" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H276" s="16" t="inlineStr">
@@ -32826,7 +32794,7 @@
       </c>
       <c r="G277" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H277" s="18" t="inlineStr">
@@ -32913,7 +32881,7 @@
       </c>
       <c r="G278" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H278" s="16" t="inlineStr">
@@ -32996,7 +32964,7 @@
       </c>
       <c r="G279" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H279" s="18" t="inlineStr">
@@ -33079,7 +33047,7 @@
       </c>
       <c r="G280" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H280" s="16" t="inlineStr">
@@ -33162,7 +33130,7 @@
       </c>
       <c r="G281" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H281" s="18" t="inlineStr">
@@ -33245,7 +33213,7 @@
       </c>
       <c r="G282" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H282" s="16" t="inlineStr">
@@ -33328,7 +33296,7 @@
       </c>
       <c r="G283" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H283" s="18" t="inlineStr">
@@ -33411,7 +33379,7 @@
       </c>
       <c r="G284" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H284" s="16" t="inlineStr">
@@ -33494,7 +33462,7 @@
       </c>
       <c r="G285" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H285" s="18" t="inlineStr">
@@ -33577,7 +33545,7 @@
       </c>
       <c r="G286" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H286" s="16" t="inlineStr">
@@ -33909,7 +33877,7 @@
       </c>
       <c r="G290" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H290" s="16" t="inlineStr">
@@ -33996,7 +33964,7 @@
       </c>
       <c r="G291" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H291" s="18" t="inlineStr">
@@ -34083,7 +34051,7 @@
       </c>
       <c r="G292" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H292" s="16" t="inlineStr">
@@ -34170,7 +34138,7 @@
       </c>
       <c r="G293" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H293" s="18" t="inlineStr">
@@ -34257,7 +34225,7 @@
       </c>
       <c r="G294" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H294" s="16" t="inlineStr">
@@ -34344,7 +34312,7 @@
       </c>
       <c r="G295" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H295" s="18" t="inlineStr">
@@ -34431,7 +34399,7 @@
       </c>
       <c r="G296" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H296" s="16" t="inlineStr">
@@ -34518,7 +34486,7 @@
       </c>
       <c r="G297" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H297" s="18" t="inlineStr">
@@ -34605,7 +34573,7 @@
       </c>
       <c r="G298" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H298" s="16" t="inlineStr">
@@ -34692,7 +34660,7 @@
       </c>
       <c r="G299" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H299" s="18" t="inlineStr">
@@ -34779,7 +34747,7 @@
       </c>
       <c r="G300" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H300" s="16" t="inlineStr">
@@ -34866,7 +34834,7 @@
       </c>
       <c r="G301" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H301" s="18" t="inlineStr">
@@ -34953,7 +34921,7 @@
       </c>
       <c r="G302" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H302" s="16" t="inlineStr">
@@ -35040,7 +35008,7 @@
       </c>
       <c r="G303" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H303" s="18" t="inlineStr">
@@ -35127,7 +35095,7 @@
       </c>
       <c r="G304" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H304" s="16" t="inlineStr">
@@ -35214,7 +35182,7 @@
       </c>
       <c r="G305" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H305" s="18" t="inlineStr">
@@ -35301,7 +35269,7 @@
       </c>
       <c r="G306" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H306" s="16" t="inlineStr">
@@ -35388,7 +35356,7 @@
       </c>
       <c r="G307" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H307" s="18" t="inlineStr">
@@ -35475,7 +35443,7 @@
       </c>
       <c r="G308" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H308" s="16" t="inlineStr">
@@ -35562,7 +35530,7 @@
       </c>
       <c r="G309" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H309" s="18" t="inlineStr">
@@ -35649,7 +35617,7 @@
       </c>
       <c r="G310" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H310" s="16" t="inlineStr">
@@ -35736,7 +35704,7 @@
       </c>
       <c r="G311" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H311" s="18" t="inlineStr">
@@ -35823,7 +35791,7 @@
       </c>
       <c r="G312" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H312" s="16" t="inlineStr">
@@ -35910,7 +35878,7 @@
       </c>
       <c r="G313" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H313" s="18" t="inlineStr">
@@ -35997,7 +35965,7 @@
       </c>
       <c r="G314" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H314" s="16" t="inlineStr">
@@ -36084,7 +36052,7 @@
       </c>
       <c r="G315" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H315" s="18" t="inlineStr">
@@ -36171,7 +36139,7 @@
       </c>
       <c r="G316" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H316" s="16" t="inlineStr">
@@ -36258,7 +36226,7 @@
       </c>
       <c r="G317" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H317" s="18" t="inlineStr">
@@ -36345,7 +36313,7 @@
       </c>
       <c r="G318" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H318" s="16" t="inlineStr">
@@ -36432,7 +36400,7 @@
       </c>
       <c r="G319" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H319" s="18" t="inlineStr">
@@ -36519,7 +36487,7 @@
       </c>
       <c r="G320" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H320" s="16" t="inlineStr">
@@ -36606,7 +36574,7 @@
       </c>
       <c r="G321" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H321" s="18" t="inlineStr">
@@ -36693,7 +36661,7 @@
       </c>
       <c r="G322" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H322" s="16" t="inlineStr">
@@ -36780,7 +36748,7 @@
       </c>
       <c r="G323" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H323" s="18" t="inlineStr">
@@ -36867,7 +36835,7 @@
       </c>
       <c r="G324" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H324" s="16" t="inlineStr">
@@ -36954,7 +36922,7 @@
       </c>
       <c r="G325" s="18" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H325" s="18" t="inlineStr">
@@ -37041,7 +37009,7 @@
       </c>
       <c r="G326" s="16" t="inlineStr">
         <is>
-          <t>(sin subgrupo)</t>
+          <t>(Sin Subgrupo)</t>
         </is>
       </c>
       <c r="H326" s="16" t="inlineStr">
